--- a/output/pdf_financials_xlsx/BSK.xlsx
+++ b/output/pdf_financials_xlsx/BSK.xlsx
@@ -1477,19 +1477,19 @@
         <v>-3.073515</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.589262</v>
+        <v>-5.589262</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.588135</v>
+        <v>-3.588135</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.251175</v>
+        <v>-1.251175</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.116683</v>
+        <v>-1.116683</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.527342</v>
+        <v>-3.527342</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1821,19 +1821,19 @@
         <v>-1.151047</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.589262</v>
+        <v>-5.589262</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.588135</v>
+        <v>-3.588135</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.251175</v>
+        <v>-1.251175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.116683</v>
+        <v>-1.116683</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.527342</v>
+        <v>-3.527342</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -2046,19 +2046,19 @@
         <v>-1.151047</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.589262</v>
+        <v>-5.589262</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.588135</v>
+        <v>-3.588135</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.251175</v>
+        <v>-1.251175</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.116683</v>
+        <v>-1.116683</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.527342</v>
+        <v>-3.527342</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -2277,19 +2277,19 @@
         <v>38.368233</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-62.102911</v>
+        <v>62.102911</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-89.70337499999999</v>
+        <v>89.70337499999999</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-15.639688</v>
+        <v>15.639688</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.427572</v>
+        <v>2.427572</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-3.296581</v>
+        <v>3.296581</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2356,19 +2356,19 @@
         <v>-3.073515</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.589262</v>
+        <v>-5.589262</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.588135</v>
+        <v>-3.588135</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.251175</v>
+        <v>-1.251175</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.116683</v>
+        <v>-1.116683</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.527342</v>
+        <v>-3.527342</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>-3.073515</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.590105</v>
+        <v>-5.588419</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.593195</v>
+        <v>-3.583075</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.262007</v>
+        <v>-1.240343</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.129919</v>
+        <v>-1.103447</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.53396</v>
+        <v>-3.520724</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2678,19 +2678,19 @@
         <v>-62.54949138039021</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -6531,52 +6531,52 @@
         <v>1.668765</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.233217</v>
+        <v>2.477291</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.467545</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.851039</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.909863</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.07668</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.07668</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.554915</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.399265</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.332186</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.730665</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.730665</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.975741</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>12.175001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>13.218381</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>13.995562</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>17.574397</v>
       </c>
     </row>
     <row r="93">
@@ -10970,7 +10970,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11904,7 +11908,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12642,7 +12650,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13262,7 +13274,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -13572,7 +13588,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14270,7 +14290,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14904,7 +14928,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -15642,7 +15670,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -16270,7 +16302,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -17432,7 +17468,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -19022,7 +19062,11 @@
           <t>Reserves 5 3,467,545</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -49360,19 +49404,19 @@
         </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>5.589262</v>
+        <v>-5.589262</v>
       </c>
       <c r="H378" s="5" t="n">
-        <v>3.588135</v>
+        <v>-3.588135</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>1.251175</v>
+        <v>-1.251175</v>
       </c>
       <c r="J378" s="5" t="n">
-        <v>1.116683</v>
+        <v>-1.116683</v>
       </c>
       <c r="K378" s="5" t="n">
-        <v>3.527342</v>
+        <v>-3.527342</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BSK.xlsx
+++ b/output/pdf_financials_xlsx/BSK.xlsx
@@ -1171,25 +1171,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.017433</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00603</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000227</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002487</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004165</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002227</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00024</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.011643</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.179382</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.009501000000000001</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.00469</v>
       </c>
     </row>
     <row r="13">
@@ -2350,25 +2350,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.217784</v>
+        <v>-7.235217</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.073515</v>
+        <v>-3.079545</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.589262</v>
+        <v>-5.589035</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.588135</v>
+        <v>-3.585648</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.251175</v>
+        <v>-1.24701</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.116683</v>
+        <v>-1.114456</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.527342</v>
+        <v>-3.527102</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.572426</v>
+        <v>-5.584069</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.65564</v>
+        <v>-3.835022</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.984861</v>
+        <v>-3.994362</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-4.277204</v>
+        <v>-4.281894</v>
       </c>
     </row>
     <row r="28">
@@ -2500,25 +2500,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.217784</v>
+        <v>-7.235217</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.073515</v>
+        <v>-3.079545</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.588419</v>
+        <v>-5.588192</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.583075</v>
+        <v>-3.580588</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.240343</v>
+        <v>-1.236178</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.103447</v>
+        <v>-1.10122</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.520724</v>
+        <v>-3.520484</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.572426</v>
+        <v>-5.584069</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.65564</v>
+        <v>-3.835022</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.984861</v>
+        <v>-3.994362</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-4.277204</v>
+        <v>-4.281894</v>
       </c>
     </row>
     <row r="30">
@@ -2851,43 +2851,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.619662</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.334398</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.334398</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.052411</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.161236</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.42681</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.053751</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005141</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.478284</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.742363</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.293079</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.360605</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.215569</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>3.287023</v>
@@ -2973,43 +2973,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.619662</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.334398</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.334398</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.052411</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.65</v>
+        <v>0.811236</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.42681</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.053751</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005141</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.478284</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.742363</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.293079</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.360605</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.215569</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>3.287023</v>
@@ -3705,43 +3705,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.702133</v>
+        <v>0.082471</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.620725</v>
+        <v>0.286327</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.670725</v>
+        <v>0.336327</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07230499999999999</v>
+        <v>0.019894</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.278226</v>
+        <v>0.11699</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.514761</v>
+        <v>0.087951</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.061931</v>
+        <v>0.00818</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.008912</v>
+        <v>0.003771</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.675213</v>
+        <v>0.196929</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.954342</v>
+        <v>0.211979</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.535079</v>
+        <v>0.242</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.407768</v>
+        <v>0.047163</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.255357</v>
+        <v>0.039788</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.08447300000000001</v>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -45390,7 +45390,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -45500,7 +45500,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -46656,7 +46656,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -49072,7 +49072,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -52766,7 +52766,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -54894,7 +54894,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E430" s="5" t="n">
